--- a/academias/Tecnologías de la Información y la Comunicación - Estadisticos 20211.xlsx
+++ b/academias/Tecnologías de la Información y la Comunicación - Estadisticos 20211.xlsx
@@ -507,25 +507,25 @@
         <v>28</v>
       </c>
       <c r="E2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>78.56999999999999</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="H2">
-        <v>21.43</v>
+        <v>10.71</v>
       </c>
       <c r="I2">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>21.43</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -542,25 +542,25 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>76.19</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H3">
-        <v>23.81</v>
+        <v>14.29</v>
       </c>
       <c r="I3">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>23.81</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -577,25 +577,25 @@
         <v>34</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>73.53</v>
+        <v>97.06</v>
       </c>
       <c r="H4">
-        <v>26.47</v>
+        <v>2.94</v>
       </c>
       <c r="I4">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="J4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>26.47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -612,25 +612,25 @@
         <v>31</v>
       </c>
       <c r="E5">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G5">
-        <v>70.97</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H5">
-        <v>29.03</v>
+        <v>19.35</v>
       </c>
       <c r="I5">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="J5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>29.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -647,25 +647,25 @@
         <v>36</v>
       </c>
       <c r="E6">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>80.56</v>
+        <v>91.67</v>
       </c>
       <c r="H6">
-        <v>19.44</v>
+        <v>8.33</v>
       </c>
       <c r="I6">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>19.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -682,25 +682,25 @@
         <v>43</v>
       </c>
       <c r="E7">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F7">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>74.42</v>
+        <v>90.7</v>
       </c>
       <c r="H7">
-        <v>25.58</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I7">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>25.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -717,25 +717,25 @@
         <v>43</v>
       </c>
       <c r="E8">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>83.72</v>
+        <v>97.67</v>
       </c>
       <c r="H8">
-        <v>16.28</v>
+        <v>2.33</v>
       </c>
       <c r="I8">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>16.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -767,10 +767,10 @@
         <v>7.3</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -799,13 +799,13 @@
         <v>22.5</v>
       </c>
       <c r="I10">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>7.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -857,25 +857,25 @@
         <v>43</v>
       </c>
       <c r="E12">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G12">
-        <v>88.37</v>
+        <v>93.02</v>
       </c>
       <c r="H12">
-        <v>11.63</v>
+        <v>6.98</v>
       </c>
       <c r="I12">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -941,22 +941,25 @@
         <v>28</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="H2">
-        <v>100</v>
+        <v>10.71</v>
+      </c>
+      <c r="I2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J2">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>100</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -973,22 +976,25 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H3">
-        <v>100</v>
+        <v>14.29</v>
+      </c>
+      <c r="I3">
+        <v>8.699999999999999</v>
       </c>
       <c r="J3">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>100</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1005,22 +1011,25 @@
         <v>34</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F4">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H4">
-        <v>100</v>
+        <v>17.65</v>
+      </c>
+      <c r="I4">
+        <v>7.4</v>
       </c>
       <c r="J4">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1037,22 +1046,25 @@
         <v>31</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>64.52</v>
       </c>
       <c r="H5">
-        <v>100</v>
+        <v>35.48</v>
+      </c>
+      <c r="I5">
+        <v>7.6</v>
       </c>
       <c r="J5">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1069,22 +1081,25 @@
         <v>36</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F6">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>80.56</v>
       </c>
       <c r="H6">
-        <v>100</v>
+        <v>19.44</v>
+      </c>
+      <c r="I6">
+        <v>8.1</v>
       </c>
       <c r="J6">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>19.44</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1101,22 +1116,25 @@
         <v>43</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F7">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H7">
-        <v>100</v>
+        <v>18.6</v>
+      </c>
+      <c r="I7">
+        <v>7.8</v>
       </c>
       <c r="J7">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1133,22 +1151,25 @@
         <v>43</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F8">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>83.72</v>
       </c>
       <c r="H8">
-        <v>100</v>
+        <v>16.28</v>
+      </c>
+      <c r="I8">
+        <v>7.4</v>
       </c>
       <c r="J8">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1165,22 +1186,25 @@
         <v>24</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F9">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H9">
-        <v>100</v>
+        <v>16.67</v>
+      </c>
+      <c r="I9">
+        <v>8.1</v>
       </c>
       <c r="J9">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1197,22 +1221,25 @@
         <v>40</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F10">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="H10">
-        <v>100</v>
+        <v>22.5</v>
+      </c>
+      <c r="I10">
+        <v>7.4</v>
       </c>
       <c r="J10">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1229,22 +1256,25 @@
         <v>44</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F11">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>95.45</v>
       </c>
       <c r="H11">
-        <v>100</v>
+        <v>4.55</v>
+      </c>
+      <c r="I11">
+        <v>7.8</v>
       </c>
       <c r="J11">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1261,22 +1291,25 @@
         <v>43</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F12">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>93.02</v>
       </c>
       <c r="H12">
-        <v>100</v>
+        <v>6.98</v>
+      </c>
+      <c r="I12">
+        <v>8.699999999999999</v>
       </c>
       <c r="J12">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1342,25 +1375,25 @@
         <v>28</v>
       </c>
       <c r="E2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>78.56999999999999</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="H2">
-        <v>21.43</v>
+        <v>10.71</v>
       </c>
       <c r="I2">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>21.43</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1377,25 +1410,25 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>76.19</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H3">
-        <v>23.81</v>
+        <v>14.29</v>
       </c>
       <c r="I3">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>23.81</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1412,25 +1445,25 @@
         <v>34</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>73.53</v>
+        <v>97.06</v>
       </c>
       <c r="H4">
-        <v>26.47</v>
+        <v>2.94</v>
       </c>
       <c r="I4">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>26.47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1447,25 +1480,25 @@
         <v>31</v>
       </c>
       <c r="E5">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G5">
-        <v>70.97</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H5">
-        <v>29.03</v>
+        <v>19.35</v>
       </c>
       <c r="I5">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>29.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1482,25 +1515,25 @@
         <v>36</v>
       </c>
       <c r="E6">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>80.56</v>
+        <v>91.67</v>
       </c>
       <c r="H6">
-        <v>19.44</v>
+        <v>8.33</v>
       </c>
       <c r="I6">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>19.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1517,25 +1550,25 @@
         <v>43</v>
       </c>
       <c r="E7">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F7">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>74.42</v>
+        <v>90.7</v>
       </c>
       <c r="H7">
-        <v>25.58</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I7">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="J7">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>25.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1552,25 +1585,25 @@
         <v>43</v>
       </c>
       <c r="E8">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>83.72</v>
+        <v>97.67</v>
       </c>
       <c r="H8">
-        <v>16.28</v>
+        <v>2.33</v>
       </c>
       <c r="I8">
         <v>7.3</v>
       </c>
       <c r="J8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>16.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1599,13 +1632,13 @@
         <v>4.17</v>
       </c>
       <c r="I9">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1637,10 +1670,10 @@
         <v>7.5</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>7.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1692,25 +1725,25 @@
         <v>43</v>
       </c>
       <c r="E12">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G12">
-        <v>88.37</v>
+        <v>93.02</v>
       </c>
       <c r="H12">
-        <v>11.63</v>
+        <v>6.98</v>
       </c>
       <c r="I12">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Tecnologías de la Información y la Comunicación - Estadisticos 20211.xlsx
+++ b/academias/Tecnologías de la Información y la Comunicación - Estadisticos 20211.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
     <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
-    <sheet name="3er Parcial" sheetId="3" r:id="rId3"/>
+    <sheet name="Final" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -100,6 +100,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -152,8 +156,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -454,42 +460,45 @@
   <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -512,19 +521,19 @@
       <c r="F2">
         <v>3</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>89.29000000000001</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>10.71</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>9</v>
       </c>
       <c r="J2">
         <v>3</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>10.71</v>
       </c>
     </row>
@@ -547,19 +556,19 @@
       <c r="F3">
         <v>3</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>85.70999999999999</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>14.29</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>8.9</v>
       </c>
       <c r="J3">
         <v>3</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>14.29</v>
       </c>
     </row>
@@ -582,19 +591,19 @@
       <c r="F4">
         <v>1</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>97.06</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>2.94</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>6.9</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -617,19 +626,19 @@
       <c r="F5">
         <v>6</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>80.65000000000001</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>19.35</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>6.8</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>0</v>
       </c>
     </row>
@@ -652,19 +661,19 @@
       <c r="F6">
         <v>3</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>91.67</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>8.33</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>7.2</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -687,19 +696,19 @@
       <c r="F7">
         <v>4</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>90.7</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>9.300000000000001</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>7</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>0</v>
       </c>
     </row>
@@ -722,19 +731,19 @@
       <c r="F8">
         <v>1</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>97.67</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>2.33</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>7.1</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>0</v>
       </c>
     </row>
@@ -757,19 +766,19 @@
       <c r="F9">
         <v>1</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>95.83</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>4.17</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>7.3</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>0</v>
       </c>
     </row>
@@ -792,19 +801,19 @@
       <c r="F10">
         <v>9</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>77.5</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>22.5</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>7.3</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0</v>
       </c>
     </row>
@@ -827,19 +836,19 @@
       <c r="F11">
         <v>2</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>95.45</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>4.55</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>8.1</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>0</v>
       </c>
     </row>
@@ -862,19 +871,19 @@
       <c r="F12">
         <v>3</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>93.02</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>6.98</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>0</v>
       </c>
     </row>
@@ -888,42 +897,45 @@
   <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -946,19 +958,19 @@
       <c r="F2">
         <v>3</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>89.29000000000001</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>10.71</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J2">
         <v>3</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>10.71</v>
       </c>
     </row>
@@ -981,19 +993,19 @@
       <c r="F3">
         <v>3</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>85.70999999999999</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>14.29</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>8.699999999999999</v>
       </c>
       <c r="J3">
         <v>3</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>14.29</v>
       </c>
     </row>
@@ -1016,19 +1028,19 @@
       <c r="F4">
         <v>6</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>82.34999999999999</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>17.65</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>7.4</v>
       </c>
       <c r="J4">
         <v>5</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>14.71</v>
       </c>
     </row>
@@ -1051,19 +1063,19 @@
       <c r="F5">
         <v>11</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>64.52</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>35.48</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>7.6</v>
       </c>
       <c r="J5">
         <v>10</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>32.26</v>
       </c>
     </row>
@@ -1086,19 +1098,19 @@
       <c r="F6">
         <v>7</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>80.56</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>19.44</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>8.1</v>
       </c>
       <c r="J6">
         <v>7</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>19.44</v>
       </c>
     </row>
@@ -1121,19 +1133,19 @@
       <c r="F7">
         <v>8</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>81.40000000000001</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>18.6</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>7.8</v>
       </c>
       <c r="J7">
         <v>8</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>18.6</v>
       </c>
     </row>
@@ -1156,19 +1168,19 @@
       <c r="F8">
         <v>7</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>83.72</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>16.28</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>7.4</v>
       </c>
       <c r="J8">
         <v>7</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>16.28</v>
       </c>
     </row>
@@ -1191,19 +1203,19 @@
       <c r="F9">
         <v>4</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>83.33</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>16.67</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>8.1</v>
       </c>
       <c r="J9">
         <v>4</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>16.67</v>
       </c>
     </row>
@@ -1226,19 +1238,19 @@
       <c r="F10">
         <v>9</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>77.5</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>22.5</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>7.4</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1261,19 +1273,19 @@
       <c r="F11">
         <v>2</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>95.45</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>4.55</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>7.8</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1296,19 +1308,19 @@
       <c r="F12">
         <v>3</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>93.02</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>6.98</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>8.699999999999999</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1322,42 +1334,45 @@
   <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1380,19 +1395,19 @@
       <c r="F2">
         <v>3</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>89.29000000000001</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>10.71</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>8.699999999999999</v>
       </c>
       <c r="J2">
         <v>3</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>10.71</v>
       </c>
     </row>
@@ -1415,19 +1430,19 @@
       <c r="F3">
         <v>3</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>85.70999999999999</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>14.29</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>9</v>
       </c>
       <c r="J3">
         <v>3</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>14.29</v>
       </c>
     </row>
@@ -1450,19 +1465,19 @@
       <c r="F4">
         <v>1</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>97.06</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>2.94</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>7.2</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1485,19 +1500,19 @@
       <c r="F5">
         <v>6</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>80.65000000000001</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>19.35</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>7.1</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1520,19 +1535,19 @@
       <c r="F6">
         <v>3</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>91.67</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>8.33</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>7.7</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1555,19 +1570,19 @@
       <c r="F7">
         <v>4</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>90.7</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>9.300000000000001</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>7.3</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1590,19 +1605,19 @@
       <c r="F8">
         <v>1</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>97.67</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>2.33</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>7.3</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1625,19 +1640,19 @@
       <c r="F9">
         <v>1</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>95.83</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>4.17</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>7.8</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1660,19 +1675,19 @@
       <c r="F10">
         <v>9</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>77.5</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>22.5</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>7.5</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1695,19 +1710,19 @@
       <c r="F11">
         <v>2</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>95.45</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>4.55</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>8.1</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1730,19 +1745,19 @@
       <c r="F12">
         <v>3</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>93.02</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>6.98</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>8.699999999999999</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>0</v>
       </c>
     </row>

--- a/academias/Tecnologías de la Información y la Comunicación - Estadisticos 20211.xlsx
+++ b/academias/Tecnologías de la Información y la Comunicación - Estadisticos 20211.xlsx
@@ -101,7 +101,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="2">

--- a/academias/Tecnologías de la Información y la Comunicación - Estadisticos 20211.xlsx
+++ b/academias/Tecnologías de la Información y la Comunicación - Estadisticos 20211.xlsx
@@ -1023,25 +1023,25 @@
         <v>34</v>
       </c>
       <c r="E4">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>82.34999999999999</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>17.65</v>
+        <v>8.82</v>
       </c>
       <c r="I4" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K4" s="1">
-        <v>14.71</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1058,25 +1058,25 @@
         <v>31</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G5" s="1">
-        <v>64.52</v>
+        <v>70.97</v>
       </c>
       <c r="H5" s="1">
-        <v>35.48</v>
+        <v>29.03</v>
       </c>
       <c r="I5" s="2">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K5" s="1">
-        <v>32.26</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1093,25 +1093,25 @@
         <v>36</v>
       </c>
       <c r="E6">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G6" s="1">
-        <v>80.56</v>
+        <v>86.11</v>
       </c>
       <c r="H6" s="1">
-        <v>19.44</v>
+        <v>13.89</v>
       </c>
       <c r="I6" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K6" s="1">
-        <v>19.44</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1128,25 +1128,25 @@
         <v>43</v>
       </c>
       <c r="E7">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G7" s="1">
-        <v>81.40000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="H7" s="1">
-        <v>18.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I7" s="2">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="J7">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>18.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1163,25 +1163,25 @@
         <v>43</v>
       </c>
       <c r="E8">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>83.72</v>
+        <v>93.02</v>
       </c>
       <c r="H8" s="1">
-        <v>16.28</v>
+        <v>6.98</v>
       </c>
       <c r="I8" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J8">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K8" s="1">
-        <v>16.28</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1198,25 +1198,25 @@
         <v>24</v>
       </c>
       <c r="E9">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>83.33</v>
+        <v>91.67</v>
       </c>
       <c r="H9" s="1">
-        <v>16.67</v>
+        <v>8.33</v>
       </c>
       <c r="I9" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K9" s="1">
-        <v>16.67</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1495,19 +1495,19 @@
         <v>31</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G5" s="1">
-        <v>80.65000000000001</v>
+        <v>77.42</v>
       </c>
       <c r="H5" s="1">
-        <v>19.35</v>
+        <v>22.58</v>
       </c>
       <c r="I5" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1542,7 +1542,7 @@
         <v>8.33</v>
       </c>
       <c r="I6" s="2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="J6">
         <v>0</v>

--- a/academias/Tecnologías de la Información y la Comunicación - Estadisticos 20211.xlsx
+++ b/academias/Tecnologías de la Información y la Comunicación - Estadisticos 20211.xlsx
@@ -516,25 +516,25 @@
         <v>28</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>89.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>10.71</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>10.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -551,25 +551,25 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -953,25 +953,25 @@
         <v>28</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>89.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>10.71</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>10.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -988,25 +988,25 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1023,25 +1023,25 @@
         <v>34</v>
       </c>
       <c r="E4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>91.18000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="H4" s="1">
-        <v>8.82</v>
+        <v>2.94</v>
       </c>
       <c r="I4" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>5.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1058,25 +1058,25 @@
         <v>31</v>
       </c>
       <c r="E5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G5" s="1">
-        <v>70.97</v>
+        <v>77.42</v>
       </c>
       <c r="H5" s="1">
-        <v>29.03</v>
+        <v>22.58</v>
       </c>
       <c r="I5" s="2">
         <v>7</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1093,25 +1093,25 @@
         <v>36</v>
       </c>
       <c r="E6">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>86.11</v>
+        <v>91.67</v>
       </c>
       <c r="H6" s="1">
-        <v>13.89</v>
+        <v>8.33</v>
       </c>
       <c r="I6" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>11.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1163,25 +1163,25 @@
         <v>43</v>
       </c>
       <c r="E8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>93.02</v>
+        <v>97.67</v>
       </c>
       <c r="H8" s="1">
-        <v>6.98</v>
+        <v>2.33</v>
       </c>
       <c r="I8" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>4.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1198,25 +1198,25 @@
         <v>24</v>
       </c>
       <c r="E9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>91.67</v>
+        <v>95.83</v>
       </c>
       <c r="H9" s="1">
-        <v>8.33</v>
+        <v>4.17</v>
       </c>
       <c r="I9" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1390,25 +1390,25 @@
         <v>28</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>89.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>10.71</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>10.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1425,25 +1425,25 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1460,19 +1460,19 @@
         <v>34</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>97.06</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1495,16 +1495,16 @@
         <v>31</v>
       </c>
       <c r="E5">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>77.42</v>
+        <v>96.77</v>
       </c>
       <c r="H5" s="1">
-        <v>22.58</v>
+        <v>3.23</v>
       </c>
       <c r="I5" s="2">
         <v>7</v>
@@ -1530,19 +1530,19 @@
         <v>36</v>
       </c>
       <c r="E6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>91.67</v>
+        <v>94.44</v>
       </c>
       <c r="H6" s="1">
-        <v>8.33</v>
+        <v>5.56</v>
       </c>
       <c r="I6" s="2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1565,19 +1565,19 @@
         <v>43</v>
       </c>
       <c r="E7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>90.7</v>
+        <v>93.02</v>
       </c>
       <c r="H7" s="1">
-        <v>9.300000000000001</v>
+        <v>6.98</v>
       </c>
       <c r="I7" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1600,19 +1600,19 @@
         <v>43</v>
       </c>
       <c r="E8">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>97.67</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>2.33</v>
+        <v>4.65</v>
       </c>
       <c r="I8" s="2">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1635,19 +1635,19 @@
         <v>24</v>
       </c>
       <c r="E9">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>95.83</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1670,19 +1670,19 @@
         <v>40</v>
       </c>
       <c r="E10">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F10">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>77.5</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
-        <v>22.5</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1705,19 +1705,19 @@
         <v>44</v>
       </c>
       <c r="E11">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>95.45</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1740,16 +1740,16 @@
         <v>43</v>
       </c>
       <c r="E12">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>93.02</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>6.98</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
         <v>8.699999999999999</v>
